--- a/artfynd/A 21244-2025 artfynd.xlsx
+++ b/artfynd/A 21244-2025 artfynd.xlsx
@@ -1868,7 +1868,7 @@
         <v>127092661</v>
       </c>
       <c r="B12" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1965,7 +1965,7 @@
         <v>127092454</v>
       </c>
       <c r="B13" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2169,7 +2169,7 @@
         <v>127103009</v>
       </c>
       <c r="B15" t="n">
-        <v>80083</v>
+        <v>80114</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>127102979</v>
       </c>
       <c r="B17" t="n">
-        <v>80112</v>
+        <v>80143</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2465,7 +2465,7 @@
         <v>127116936</v>
       </c>
       <c r="B18" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2664,7 +2664,7 @@
         <v>127116856</v>
       </c>
       <c r="B20" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>127145489</v>
       </c>
       <c r="B21" t="n">
-        <v>79004</v>
+        <v>79035</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 21244-2025 artfynd.xlsx
+++ b/artfynd/A 21244-2025 artfynd.xlsx
@@ -1868,7 +1868,7 @@
         <v>127092661</v>
       </c>
       <c r="B12" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1965,7 +1965,7 @@
         <v>127092454</v>
       </c>
       <c r="B13" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2169,7 +2169,7 @@
         <v>127103009</v>
       </c>
       <c r="B15" t="n">
-        <v>80114</v>
+        <v>80117</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>127102979</v>
       </c>
       <c r="B17" t="n">
-        <v>80143</v>
+        <v>80146</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2465,7 +2465,7 @@
         <v>127116936</v>
       </c>
       <c r="B18" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2664,7 +2664,7 @@
         <v>127116856</v>
       </c>
       <c r="B20" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>127145489</v>
       </c>
       <c r="B21" t="n">
-        <v>79035</v>
+        <v>79038</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 21244-2025 artfynd.xlsx
+++ b/artfynd/A 21244-2025 artfynd.xlsx
@@ -1865,7 +1865,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127092661</v>
+        <v>127092454</v>
       </c>
       <c r="B12" t="n">
         <v>79014</v>
@@ -1900,10 +1900,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>592188</v>
+        <v>592149</v>
       </c>
       <c r="R12" t="n">
-        <v>6984807</v>
+        <v>6984914</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1962,7 +1962,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127092454</v>
+        <v>127092661</v>
       </c>
       <c r="B13" t="n">
         <v>79014</v>
@@ -1997,10 +1997,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>592149</v>
+        <v>592188</v>
       </c>
       <c r="R13" t="n">
-        <v>6984914</v>
+        <v>6984807</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 21244-2025 artfynd.xlsx
+++ b/artfynd/A 21244-2025 artfynd.xlsx
@@ -1865,7 +1865,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127092454</v>
+        <v>127092661</v>
       </c>
       <c r="B12" t="n">
         <v>79014</v>
@@ -1900,10 +1900,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>592149</v>
+        <v>592188</v>
       </c>
       <c r="R12" t="n">
-        <v>6984914</v>
+        <v>6984807</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1962,7 +1962,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127092661</v>
+        <v>127092454</v>
       </c>
       <c r="B13" t="n">
         <v>79014</v>
@@ -1997,10 +1997,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>592188</v>
+        <v>592149</v>
       </c>
       <c r="R13" t="n">
-        <v>6984807</v>
+        <v>6984914</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 21244-2025 artfynd.xlsx
+++ b/artfynd/A 21244-2025 artfynd.xlsx
@@ -1865,10 +1865,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127092661</v>
+        <v>127092454</v>
       </c>
       <c r="B12" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1900,10 +1900,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>592188</v>
+        <v>592149</v>
       </c>
       <c r="R12" t="n">
-        <v>6984807</v>
+        <v>6984914</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1962,10 +1962,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127092454</v>
+        <v>127092661</v>
       </c>
       <c r="B13" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1997,10 +1997,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>592149</v>
+        <v>592188</v>
       </c>
       <c r="R13" t="n">
-        <v>6984914</v>
+        <v>6984807</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2062,7 +2062,7 @@
         <v>127100118</v>
       </c>
       <c r="B14" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2169,7 +2169,7 @@
         <v>127103009</v>
       </c>
       <c r="B15" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2266,7 +2266,7 @@
         <v>127092509</v>
       </c>
       <c r="B16" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>127102979</v>
       </c>
       <c r="B17" t="n">
-        <v>80146</v>
+        <v>80150</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2465,7 +2465,7 @@
         <v>127116936</v>
       </c>
       <c r="B18" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2562,7 +2562,7 @@
         <v>127116965</v>
       </c>
       <c r="B19" t="n">
-        <v>57817</v>
+        <v>57821</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2664,7 +2664,7 @@
         <v>127116856</v>
       </c>
       <c r="B20" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>127145489</v>
       </c>
       <c r="B21" t="n">
-        <v>79038</v>
+        <v>79042</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 21244-2025 artfynd.xlsx
+++ b/artfynd/A 21244-2025 artfynd.xlsx
@@ -1865,7 +1865,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127092454</v>
+        <v>127092661</v>
       </c>
       <c r="B12" t="n">
         <v>79018</v>
@@ -1900,10 +1900,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>592149</v>
+        <v>592188</v>
       </c>
       <c r="R12" t="n">
-        <v>6984914</v>
+        <v>6984807</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1962,7 +1962,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127092661</v>
+        <v>127092454</v>
       </c>
       <c r="B13" t="n">
         <v>79018</v>
@@ -1997,10 +1997,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>592188</v>
+        <v>592149</v>
       </c>
       <c r="R13" t="n">
-        <v>6984807</v>
+        <v>6984914</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 21244-2025 artfynd.xlsx
+++ b/artfynd/A 21244-2025 artfynd.xlsx
@@ -1868,7 +1868,7 @@
         <v>127092661</v>
       </c>
       <c r="B12" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1965,7 +1965,7 @@
         <v>127092454</v>
       </c>
       <c r="B13" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2062,7 +2062,7 @@
         <v>127100118</v>
       </c>
       <c r="B14" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2169,7 +2169,7 @@
         <v>127103009</v>
       </c>
       <c r="B15" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2266,7 +2266,7 @@
         <v>127092509</v>
       </c>
       <c r="B16" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>127102979</v>
       </c>
       <c r="B17" t="n">
-        <v>80150</v>
+        <v>80152</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2465,7 +2465,7 @@
         <v>127116936</v>
       </c>
       <c r="B18" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2562,7 +2562,7 @@
         <v>127116965</v>
       </c>
       <c r="B19" t="n">
-        <v>57821</v>
+        <v>57823</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2664,7 +2664,7 @@
         <v>127116856</v>
       </c>
       <c r="B20" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>127145489</v>
       </c>
       <c r="B21" t="n">
-        <v>79042</v>
+        <v>79044</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 21244-2025 artfynd.xlsx
+++ b/artfynd/A 21244-2025 artfynd.xlsx
@@ -1865,10 +1865,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127092661</v>
+        <v>127092454</v>
       </c>
       <c r="B12" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1900,10 +1900,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>592188</v>
+        <v>592149</v>
       </c>
       <c r="R12" t="n">
-        <v>6984807</v>
+        <v>6984914</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1962,10 +1962,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127092454</v>
+        <v>127092661</v>
       </c>
       <c r="B13" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1997,10 +1997,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>592149</v>
+        <v>592188</v>
       </c>
       <c r="R13" t="n">
-        <v>6984914</v>
+        <v>6984807</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2062,7 +2062,7 @@
         <v>127100118</v>
       </c>
       <c r="B14" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2169,7 +2169,7 @@
         <v>127103009</v>
       </c>
       <c r="B15" t="n">
-        <v>80123</v>
+        <v>80126</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2266,7 +2266,7 @@
         <v>127092509</v>
       </c>
       <c r="B16" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>127102979</v>
       </c>
       <c r="B17" t="n">
-        <v>80152</v>
+        <v>80155</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2465,7 +2465,7 @@
         <v>127116936</v>
       </c>
       <c r="B18" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2562,7 +2562,7 @@
         <v>127116965</v>
       </c>
       <c r="B19" t="n">
-        <v>57823</v>
+        <v>57826</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2664,7 +2664,7 @@
         <v>127116856</v>
       </c>
       <c r="B20" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>127145489</v>
       </c>
       <c r="B21" t="n">
-        <v>79044</v>
+        <v>79047</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 21244-2025 artfynd.xlsx
+++ b/artfynd/A 21244-2025 artfynd.xlsx
@@ -1868,7 +1868,7 @@
         <v>127092454</v>
       </c>
       <c r="B12" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1965,7 +1965,7 @@
         <v>127092661</v>
       </c>
       <c r="B13" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2062,7 +2062,7 @@
         <v>127100118</v>
       </c>
       <c r="B14" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2169,7 +2169,7 @@
         <v>127103009</v>
       </c>
       <c r="B15" t="n">
-        <v>80126</v>
+        <v>80132</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2266,7 +2266,7 @@
         <v>127092509</v>
       </c>
       <c r="B16" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>127102979</v>
       </c>
       <c r="B17" t="n">
-        <v>80155</v>
+        <v>80161</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2465,7 +2465,7 @@
         <v>127116936</v>
       </c>
       <c r="B18" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2562,7 +2562,7 @@
         <v>127116965</v>
       </c>
       <c r="B19" t="n">
-        <v>57826</v>
+        <v>57832</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2664,7 +2664,7 @@
         <v>127116856</v>
       </c>
       <c r="B20" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>127145489</v>
       </c>
       <c r="B21" t="n">
-        <v>79047</v>
+        <v>79053</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 21244-2025 artfynd.xlsx
+++ b/artfynd/A 21244-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2857,6 +2857,103 @@
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>129431320</v>
+      </c>
+      <c r="B22" t="n">
+        <v>80148</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Ödingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>592041</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6984857</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 21244-2025 artfynd.xlsx
+++ b/artfynd/A 21244-2025 artfynd.xlsx
@@ -2862,7 +2862,7 @@
         <v>129431320</v>
       </c>
       <c r="B22" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 21244-2025 artfynd.xlsx
+++ b/artfynd/A 21244-2025 artfynd.xlsx
@@ -2862,7 +2862,7 @@
         <v>129431320</v>
       </c>
       <c r="B22" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
